--- a/[服務商優惠徵集 ] 智造在台灣6.0 & 亞馬遜新銳品牌加速器2.0 (Responses)(2).xlsx
+++ b/[服務商優惠徵集 ] 智造在台灣6.0 & 亞馬遜新銳品牌加速器2.0 (Responses)(2).xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanniel\OneDrive - amazon.com\桌面\2025 Q4 SSP benefits\Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3FE3EB-CB30-449E-9EC7-B4302C9FEEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50F2DDE-0377-4789-B11B-C4C46079283E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="218">
   <si>
     <t>您的姓名</t>
   </si>
@@ -117,12 +130,6 @@
     <t>https://drive.google.com/open?id=1dQlTs_mlvIH6vXSc3JzxkzMNuY30Xod2</t>
   </si>
   <si>
-    <t>0975127727</t>
-  </si>
-  <si>
-    <t>a93324u</t>
-  </si>
-  <si>
     <t>https://drive.google.com/open?id=1EvCCIqyjbV9U707ckxCxQrOJxgFGDEiF</t>
   </si>
   <si>
@@ -153,12 +160,6 @@
     <t>https://drive.google.com/open?id=1zc60MfP-oCFQM1ihfmNuRyR0GkCo2tRq</t>
   </si>
   <si>
-    <t>吳廷萱</t>
-  </si>
-  <si>
-    <t>lindawu1969@gmail.com</t>
-  </si>
-  <si>
     <t>靈志科技有限公司</t>
   </si>
   <si>
@@ -177,32 +178,7 @@
     <t>lindawu1969</t>
   </si>
   <si>
-    <t>張永淑</t>
-  </si>
-  <si>
-    <t>chris.chang@sellervantage.com.tw</t>
-  </si>
-  <si>
-    <t>全球賣跨境電商</t>
-  </si>
-  <si>
     <t>代營運</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1MLzNFQYW34FG_yJ4m9Dr9G1Bbt1jQuQE</t>
-  </si>
-  <si>
-    <t>Seller Vantage 全球賣：集團賦能，全球市場領航者
-隸屬唯數集團旗下，專精於跨境電商領域的策略性業務核心，我們憑藉集團深厚的數位營運與全球市場拓展實力，致力於為合作夥伴精準佈局國際電商版圖，實現品牌影響力與市場銷售的雙重躍升。</t>
-  </si>
-  <si>
-    <t>https://www.sellervantage.com.tw/ourservices/</t>
-  </si>
-  <si>
-    <t>0929339312</t>
-  </si>
-  <si>
-    <t>chris_c.</t>
   </si>
   <si>
     <t>童寶慶</t>
@@ -462,9 +438,6 @@
   </si>
   <si>
     <t>https://www.drs.network/</t>
-  </si>
-  <si>
-    <t>善恩創新股份有限公司(窗口：郭冠均 Rovi Kuo)</t>
   </si>
   <si>
     <t>https://drive.google.com/open?id=1kIPguigMd5HMEEskgFn5L8opS2baeGYw, https://drive.google.com/open?id=1aTM10mGpnMMyZf_Z0WLEZoHCLpdwOpQs</t>
@@ -505,9 +478,6 @@
     <t>https://drive.google.com/open?id=1V0q6EtvdSpDOGOjv_21k6-LMTEDE5iss</t>
   </si>
   <si>
-    <t>909-235-6253</t>
-  </si>
-  <si>
     <t>洪銘言 Frank</t>
   </si>
   <si>
@@ -542,25 +512,13 @@
 https://trb.one/Seller-Boost-Camp</t>
   </si>
   <si>
-    <t>商品Listing撰寫服務優惠價$13,000元/SKU (原價:$15,000元/SKU)</t>
-  </si>
-  <si>
-    <t>前三個月月費$19,999元/月(原價:$55,000元/月)。廣告抽成前三個月2.5%(原價5%)。</t>
-  </si>
-  <si>
     <t>商品頁內容優化方案，協助您進行視覺內容企劃，並執行產品競品分析，進一步撰寫圖片文案，客製化設計產品主子圖與 Basic A+: 優惠價$59,999元 (原價$65,000元)</t>
   </si>
   <si>
     <t>產品合規</t>
   </si>
   <si>
-    <t>(以下圖片點擊放大)</t>
-  </si>
-  <si>
     <t>VAT申請</t>
-  </si>
-  <si>
-    <t>陪跑教練方案 買3個月就送1個月(原價13,500/月, 專屬優惠相當於75折)</t>
   </si>
   <si>
     <t>9折優惠: 
@@ -571,9 +529,6 @@
   <si>
     <t>(限美、日站）  
 為已完成品牌註冊的新賣家，提供從新品刊登上架到完整Listing 企劃製作的Starter頁面建置方案，單次組合之早鳥方案價 NT$ 33000 起；若需求包含出貨、品牌館或廣告基礎設置，加購後可享整體專案優惠 9 折。另有商品商業照片＆影片攝影(包含素材製作)的專屬優惠。</t>
-  </si>
-  <si>
-    <t>跨境物流</t>
   </si>
   <si>
     <t>品牌素材製作</t>
@@ -592,9 +547,6 @@
 [新加坡]
 新加坡商標申請每類 優惠價格 新台幣 17,000元（未稅）[新台幣 19,000元（未稅）]
 新加坡商標領證每類 優惠價格 新台幣 2,000元（未稅）[新台幣 3,000元（未稅）]</t>
-  </si>
-  <si>
-    <t>品牌優化方案 75折, 詳情請點擊放大圖片</t>
   </si>
   <si>
     <t>亞馬遜優惠價 -$100美金 / 件 
@@ -763,12 +715,117 @@
 • 享受Payoneer 跨境生態圈服務, 快速連接1000+ 大中華區跨境電商服務商, 超20+ Payoneer 網內閉環直付
 請填寫表單開通優惠費率: https://reurl.cc/bmKY8d</t>
   </si>
+  <si>
+    <t>02-2545-8780</t>
+  </si>
+  <si>
+    <t>@viewec</t>
+  </si>
+  <si>
+    <t>Linda Wu</t>
+  </si>
+  <si>
+    <t>lindawu1969@gmail.com
+lindawu@chancevideos.com</t>
+  </si>
+  <si>
+    <t>郭冠均 Rovi Kuo</t>
+  </si>
+  <si>
+    <t>Kent</t>
+  </si>
+  <si>
+    <t>kent.he@dolphin-gp.com</t>
+  </si>
+  <si>
+    <t>泰電國際</t>
+  </si>
+  <si>
+    <t>1) 0-1孵化器專案NTD: 30,000 (一次服務方案)
+2) 廣告投放專案NTD: 15,000/月 (最短合作時間需3個月)</t>
+  </si>
+  <si>
+    <t>https://dolphinecommerce.com/</t>
+  </si>
+  <si>
+    <t>泰電國際DolphinEC為萬泰物流全資子公司，泰電國際是全球電商與物流的領導者，我們擁有多元產業的Amazon代營運經驗，強大的陸海空運輸能力與行銷網路，提供您一站式整合服務。
+我們的海外倉庫能確保您在旺季補貨無阻，透過整合行銷服務網路，能讓您在多元渠道高效曝光，提升銷售並建立國際品牌形象。</t>
+  </si>
+  <si>
+    <t>0905070150</t>
+  </si>
+  <si>
+    <t>亞馬遜文案升級包：協助您優化品牌提升視覺一致性，原價15,000元 ，專屬優惠價:10,000元。, 詳情請點擊放大圖片</t>
+  </si>
+  <si>
+    <t>亞馬遜陪跑教練方案：教練會依據需要登入賣家帳戶觀察，督促進度並提出滾動式建議。成立獨立 Line 群組，發現問題立即通知，並提供處理方法讓您的營運人員執行。原價13,500/月，買3個月就送1個月(75折優惠) 。</t>
+  </si>
+  <si>
+    <t>營運顧問</t>
+  </si>
+  <si>
+    <t>跨境電商入門學：優惠價折500台幣，原價： 12,000 台幣 https://ppa.tw/s/9A6839CA  (以下圖片點擊放大)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0958-652-960 </t>
+  </si>
+  <si>
+    <t>【美國站跨境入門優惠方案】 專為美國市場拓展打造，現省 20 萬，加速啟動跨境布局！
+專案價格： $36,000 + 3% 服務抽成/月
+專案對象：新銳品牌加速器、陪跑企劃賣家
+核心服務：亞馬遜美國站管理、動態監控、市場調研與競品分析。
+品牌優化：精準文案與關鍵字佈局、品牌申請規劃、專業外文客服。
+驚喜加碼： 免費協助建置英國、加拿大、澳洲、中東（UAE）四擇一站點。
+價值增值： 積極對接政府補助資源中，細節確認後將第一時間為本方案客戶優先配對。
+【日本站跨境入門優惠方案】專為拓展日本市場打造，現省 20 萬，加速啟動跨境布局！
+專案價格： $36,000 + 3% 服務抽成/月
+專案對象：新銳品牌加速器、陪跑企劃賣家
+核心服務：日本站管理、動態監控、市場調研與競品分析。
+品牌優化：精準文案與關鍵字佈局、品牌申請規劃、專業外文客服。
+驚喜加碼： 日本 TikTok 免費 1 年上架曝光行銷。
+價值增值： 積極對接政府補助資源中，細節確認後將第一時間為本方案客戶優先配對。</t>
+  </si>
+  <si>
+    <t>跨境物流 &amp; 海外倉</t>
+  </si>
+  <si>
+    <t>① AI影像廣告素材:NT$12,000/支 (企劃一次修改,AI完整生成)
+② 創意影音(依腳本內容定價)
+(以下圖片點擊放大)</t>
+  </si>
+  <si>
+    <t>EENuRetail 壹壹新零售</t>
+  </si>
+  <si>
+    <t>我們專注數據化、智能化的電商運營及媒體成效，並開創新型態TSP (Trade-Service-Partnership) 貿易型服務夥伴模式，協助合作夥伴零門檻打開國際市場，結合傳統貿易與專業服務，依照工廠不同狀態與需求，提供雙贏合作路徑 (亞馬遜運營服務 / B2C選物通路貿易 / B2B代工貼牌貿易)，協助台灣製造業工廠與品牌快速打開國際市場。</t>
+  </si>
+  <si>
+    <t>https://eenuretail.com/</t>
+  </si>
+  <si>
+    <t>Cindy</t>
+  </si>
+  <si>
+    <t>cindy@eenuretail.com</t>
+  </si>
+  <si>
+    <t>(以下圖片點擊放大)
+專案類型	走期天數	策略目標
+【流量啟動專案】	60天	快速測品、獲取首波數據
+【滾動穩健專案】	90天	穩型優化、擴張受眾規模
+【品牌全域專案】	180天	多點佈局、提升獲客成本
+限時促銷活動
+① 1/21-1/23 簽約 享 服務費10%
+② 陪跑計劃期間內簽約 享 服務費12%
+③ 指定Amazon DSP 獨立加碼 US$3,199 贈《AI影音廣告素材》一支
+註1:報價簽完後需一個月內儲值 註2:儲值金保有一年效益,專案經啟動後,天數不可中斷 註3:非促銷活動內,服務費一律15%</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -840,6 +897,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -849,7 +930,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -988,11 +1069,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF442F65"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1085,9 +1175,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1118,6 +1205,26 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1220,10 +1327,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:L27" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A1:L27" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L27">
-    <sortCondition ref="D1:D27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:L28" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L28" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L28">
+    <sortCondition ref="D1:D28"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="您的姓名" dataDxfId="11"/>
@@ -1444,11 +1551,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18.90625" customWidth="1"/>
-    <col min="5" max="5" width="56" style="16" customWidth="1"/>
+    <col min="5" max="5" width="66.7265625" style="16" customWidth="1"/>
     <col min="6" max="6" width="31" customWidth="1"/>
     <col min="7" max="8" width="18.90625" customWidth="1"/>
     <col min="9" max="9" width="23.08984375" customWidth="1"/>
@@ -1495,949 +1602,1002 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="H3" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="I3" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="J3" s="8" t="s">
+    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="F2" s="29"/>
+      <c r="G2" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="I3" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="J3" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="L3" s="43"/>
+    </row>
+    <row r="4" spans="1:12" ht="237.5" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" s="24"/>
+      <c r="G4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="44" t="s">
+        <v>192</v>
+      </c>
+      <c r="K4" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="F5" s="24"/>
+      <c r="G5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="I5" s="24"/>
+      <c r="J5" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="1:12" ht="62.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12" ht="87.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="L5" s="10"/>
-    </row>
-    <row r="6" spans="1:12" ht="125" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="C6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>16</v>
+        <v>130</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="25" t="s">
-        <v>19</v>
+        <v>133</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>134</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="10"/>
-    </row>
-    <row r="7" spans="1:12" ht="50" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="13" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>176</v>
+        <v>112</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>130</v>
+        <v>114</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" spans="1:12" ht="13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="162.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>100</v>
+        <v>215</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>104</v>
+        <v>216</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>212</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>217</v>
+      </c>
+      <c r="F8" s="49"/>
+      <c r="G8" s="48" t="s">
+        <v>213</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="I8" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="I8" s="51"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="53"/>
+    </row>
+    <row r="9" spans="1:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="10"/>
+    </row>
+    <row r="10" spans="1:12" ht="50" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="J8" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="C10" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" ht="50" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="L9" s="10"/>
-    </row>
-    <row r="10" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="27" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="13" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L11" s="10"/>
+    </row>
+    <row r="12" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="44" t="s">
+        <v>192</v>
+      </c>
+      <c r="K12" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="L12" s="27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C13" s="47" t="s">
+        <v>212</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="F13" s="24"/>
+      <c r="G13" s="48" t="s">
+        <v>213</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="I13" s="24"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="27"/>
+    </row>
+    <row r="14" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="K14" s="1"/>
+      <c r="L14" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="50" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K15" s="4"/>
+      <c r="L15" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="K16" s="1"/>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="1:12" ht="312.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="L11" s="10"/>
-    </row>
-    <row r="12" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E12" s="14" t="s">
+      <c r="D17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="10"/>
+    </row>
+    <row r="18" spans="1:12" ht="50" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="F18" s="34"/>
+      <c r="G18" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="H18" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="I18" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="J18" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="L18" s="31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="137.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="K12" s="1"/>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" ht="312.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="10"/>
-    </row>
-    <row r="14" spans="1:12" ht="50" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="F14" s="35"/>
-      <c r="G14" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="H14" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="I14" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="J14" s="30" t="s">
-        <v>199</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="L14" s="31" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="137.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="F15" s="36"/>
-      <c r="G15" s="17" t="s">
-        <v>206</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="I15" s="36"/>
-      <c r="J15" s="41" t="s">
+      <c r="B19" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="F19" s="35"/>
+      <c r="G19" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="I19" s="35"/>
+      <c r="J19" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="L19" s="42" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="13" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="L20" s="28" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="25" x14ac:dyDescent="0.35">
+      <c r="A21" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="F21" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="H21" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="J21" s="45" t="s">
         <v>208</v>
       </c>
-      <c r="K15" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="L15" s="43" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="I16" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K16" s="4"/>
-      <c r="L16" s="26" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="125.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="K21" s="11">
+        <v>8166826864</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="I22" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K22" s="4"/>
+      <c r="L22" s="26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="125.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H18" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="I18" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L18" s="26" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="13" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="H20" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="I20" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="K20" s="4"/>
-      <c r="L20" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="137.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="F21" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="K21" s="1"/>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="1:12" ht="150" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="E22" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="K22" s="4"/>
-      <c r="L22" s="10"/>
-    </row>
-    <row r="23" spans="1:12" ht="137.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="K23" s="4"/>
-      <c r="L23" s="10"/>
-    </row>
-    <row r="24" spans="1:12" ht="13" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="D24" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>134</v>
+        <v>152</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>154</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>137</v>
+        <v>33</v>
+      </c>
+      <c r="H24" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" s="25" t="s">
+        <v>35</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>138</v>
+        <v>36</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="L24" s="28" t="s">
-        <v>140</v>
+        <v>37</v>
+      </c>
+      <c r="L24" s="26" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C25" s="11" t="s">
+      <c r="A25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="D25" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="F25" s="37" t="s">
+      <c r="E25" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="K25" s="1"/>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="1:12" ht="125" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="G25" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="H25" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="I25" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="J25" s="11" t="s">
+      <c r="E26" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="1:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K27" s="4"/>
+      <c r="L27" s="10"/>
+    </row>
+    <row r="28" spans="1:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K28" s="4"/>
+      <c r="L28" s="10"/>
+    </row>
+    <row r="29" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="K25" s="11">
-        <v>8166826864</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="4" t="s">
+      <c r="E29" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F29" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E26" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="F26" s="29"/>
-      <c r="G26" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="L26" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="B27" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="C27" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="D27" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="G27" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="H27" s="38" t="s">
-        <v>162</v>
-      </c>
-      <c r="I27" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="J27" s="42" t="s">
-        <v>164</v>
-      </c>
-      <c r="K27" s="34" t="s">
-        <v>165</v>
-      </c>
-      <c r="L27" s="44"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="H10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="I10" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="L10" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="H18" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="I18" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="L18" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="H11" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="F16" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="H16" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="I16" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="L16" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="H13" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="H26" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="I26" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="L26" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="F2" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="I2" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="F19" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="I19" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="F21" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="I21" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="F22" r:id="rId23" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="I22" r:id="rId24" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="F23" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="I23" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="F20" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="H20" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="I20" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="F8" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="H8" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="I8" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="F17" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="H17" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="I17" r:id="rId35" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="L17" r:id="rId36" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="H3" r:id="rId37" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="I3" r:id="rId38" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="H24" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="I24" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="L24" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="H4" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="I4" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="L4" r:id="rId44" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="F25" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="H25" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="I25" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="H27" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="I27" r:id="rId49" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="F5" r:id="rId50" xr:uid="{9621AAF6-1AEF-45B6-948B-8A200C55F54F}"/>
-    <hyperlink ref="H5" r:id="rId51" xr:uid="{F05B6393-0AEA-45AE-8F51-70B7DB7C6707}"/>
-    <hyperlink ref="F6" r:id="rId52" xr:uid="{48EF63BD-F6F8-400A-92FD-B3AFAB4C0B7A}"/>
-    <hyperlink ref="H6" r:id="rId53" xr:uid="{3A5A7569-8643-4E45-85ED-60174D4E5CB6}"/>
-    <hyperlink ref="I6" r:id="rId54" xr:uid="{3139C50B-8487-4567-8D9E-7C8A851ED9B8}"/>
-    <hyperlink ref="H7" r:id="rId55" xr:uid="{6E2BDC3B-722A-4B9A-AD97-DEE9516ECCB8}"/>
-    <hyperlink ref="I7" r:id="rId56" xr:uid="{280FDD34-40EE-4A37-A829-29F6BD192708}"/>
-    <hyperlink ref="H9" r:id="rId57" xr:uid="{C4F6B81D-8AF1-4F6B-914D-0735D0E4A351}"/>
-    <hyperlink ref="F12" r:id="rId58" xr:uid="{F1485982-E543-45EF-AAB4-3B75055623A2}"/>
-    <hyperlink ref="I12" r:id="rId59" xr:uid="{4FE4C3E4-738A-4E7C-98C4-6B52004A2E77}"/>
-    <hyperlink ref="H14" r:id="rId60" xr:uid="{549F0BB1-0F01-4B7A-AE05-D916D6DEA7DC}"/>
-    <hyperlink ref="I14" r:id="rId61" xr:uid="{330DCD4E-10C6-4434-B8EA-E295B2B5FDF3}"/>
-    <hyperlink ref="L14" r:id="rId62" xr:uid="{88418B46-64A5-45A1-845A-C2EE40C5E1B5}"/>
-    <hyperlink ref="H15" r:id="rId63" xr:uid="{31EB320F-B606-452E-9151-73E76ADA829D}"/>
-    <hyperlink ref="L15" r:id="rId64" xr:uid="{C4CB046D-1B1F-4C32-93CD-E40C2A4E2CD7}"/>
+    <hyperlink ref="F12" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="H12" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="I12" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="L12" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="H24" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="I24" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="L24" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="F22" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="H22" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="I22" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="L22" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="H17" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="F25" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="I25" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="F26" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="I26" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="F27" r:id="rId17" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="I27" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="F28" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="I28" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="F23" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="H23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="I23" r:id="rId23" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="L23" r:id="rId24" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="H7" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="I7" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="F9" r:id="rId27" xr:uid="{48EF63BD-F6F8-400A-92FD-B3AFAB4C0B7A}"/>
+    <hyperlink ref="H9" r:id="rId28" xr:uid="{3A5A7569-8643-4E45-85ED-60174D4E5CB6}"/>
+    <hyperlink ref="I9" r:id="rId29" xr:uid="{3139C50B-8487-4567-8D9E-7C8A851ED9B8}"/>
+    <hyperlink ref="H10" r:id="rId30" xr:uid="{6E2BDC3B-722A-4B9A-AD97-DEE9516ECCB8}"/>
+    <hyperlink ref="I10" r:id="rId31" xr:uid="{280FDD34-40EE-4A37-A829-29F6BD192708}"/>
+    <hyperlink ref="H11" r:id="rId32" xr:uid="{C4F6B81D-8AF1-4F6B-914D-0735D0E4A351}"/>
+    <hyperlink ref="F16" r:id="rId33" xr:uid="{F1485982-E543-45EF-AAB4-3B75055623A2}"/>
+    <hyperlink ref="I16" r:id="rId34" xr:uid="{4FE4C3E4-738A-4E7C-98C4-6B52004A2E77}"/>
+    <hyperlink ref="H18" r:id="rId35" xr:uid="{549F0BB1-0F01-4B7A-AE05-D916D6DEA7DC}"/>
+    <hyperlink ref="I18" r:id="rId36" xr:uid="{330DCD4E-10C6-4434-B8EA-E295B2B5FDF3}"/>
+    <hyperlink ref="L18" r:id="rId37" xr:uid="{88418B46-64A5-45A1-845A-C2EE40C5E1B5}"/>
+    <hyperlink ref="H19" r:id="rId38" xr:uid="{31EB320F-B606-452E-9151-73E76ADA829D}"/>
+    <hyperlink ref="L19" r:id="rId39" xr:uid="{C4CB046D-1B1F-4C32-93CD-E40C2A4E2CD7}"/>
+    <hyperlink ref="H4" r:id="rId40" xr:uid="{00D3FD4F-8301-4F9C-BD25-085F343AF400}"/>
+    <hyperlink ref="I4" r:id="rId41" xr:uid="{77972CD5-5235-4508-99A2-D9EBF9B5D649}"/>
+    <hyperlink ref="H2" r:id="rId42" xr:uid="{A0F3FBFA-CA07-4AC6-9EC1-84C5C129132C}"/>
+    <hyperlink ref="I2" r:id="rId43" xr:uid="{64856348-85CB-4AE2-A1C0-0B27E6607F87}"/>
+    <hyperlink ref="L2" r:id="rId44" xr:uid="{17FCC39C-2ED1-4CC1-99B2-BD3F94DCC553}"/>
+    <hyperlink ref="H3" r:id="rId45" xr:uid="{D66A9414-072E-4D32-81BF-E39877681AA9}"/>
+    <hyperlink ref="I3" r:id="rId46" xr:uid="{3FB74EDA-8788-459D-81E9-9A39EFE58630}"/>
+    <hyperlink ref="F29" r:id="rId47" xr:uid="{F8FA01F2-473F-4541-BDBA-F4094D1A71A2}"/>
+    <hyperlink ref="I29" r:id="rId48" xr:uid="{E8031DCE-ADC1-4E45-82B2-D92828E1645D}"/>
+    <hyperlink ref="H6" r:id="rId49" xr:uid="{0641293A-8641-46FD-B579-FA3CBC9DADB8}"/>
+    <hyperlink ref="I6" r:id="rId50" xr:uid="{E62DD99D-7E76-46A6-B0C2-CF71C6BC07BE}"/>
+    <hyperlink ref="L6" r:id="rId51" xr:uid="{D6F3CDD2-D72D-493A-B523-CFF8CE0CDA62}"/>
+    <hyperlink ref="F14" r:id="rId52" xr:uid="{ECEDD51E-3EF1-4DA5-8D9D-7CB17AAFF488}"/>
+    <hyperlink ref="H14" r:id="rId53" xr:uid="{303FDBAE-996E-4C59-A99E-7EDA0B44A4DA}"/>
+    <hyperlink ref="I14" r:id="rId54" xr:uid="{6A25F310-C2F8-4ECD-BDF0-1E9ADC065A8E}"/>
+    <hyperlink ref="F15" r:id="rId55" xr:uid="{6ECC78D5-EFEC-4F41-B83D-3BA2211CF6CB}"/>
+    <hyperlink ref="H15" r:id="rId56" xr:uid="{2BF38F9B-1105-43B9-B776-F76F8F9A8415}"/>
+    <hyperlink ref="I15" r:id="rId57" xr:uid="{8D15103F-582F-4A1B-BF32-34AFE0BB24B1}"/>
+    <hyperlink ref="H20" r:id="rId58" xr:uid="{91402AEF-AB63-4FCF-83EE-1CD55B337F24}"/>
+    <hyperlink ref="I20" r:id="rId59" xr:uid="{37794728-F846-4337-A839-51CC86742FAD}"/>
+    <hyperlink ref="L20" r:id="rId60" xr:uid="{B31C2EFE-7F32-4AFE-9359-09673871A264}"/>
+    <hyperlink ref="F21" r:id="rId61" xr:uid="{2F84B398-5457-4956-B4F4-37FE84022D7D}"/>
+    <hyperlink ref="H21" r:id="rId62" xr:uid="{20546359-6976-4E54-8447-3390BAD6BD2E}"/>
+    <hyperlink ref="I21" r:id="rId63" xr:uid="{81D6B89C-0C30-47B4-80E0-4BD5EEABA76A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId65"/>
+  <pageSetup orientation="portrait" r:id="rId64"/>
   <tableParts count="1">
-    <tablePart r:id="rId66"/>
+    <tablePart r:id="rId65"/>
   </tableParts>
 </worksheet>
 </file>
--- a/[服務商優惠徵集 ] 智造在台灣6.0 & 亞馬遜新銳品牌加速器2.0 (Responses)(2).xlsx
+++ b/[服務商優惠徵集 ] 智造在台灣6.0 & 亞馬遜新銳品牌加速器2.0 (Responses)(2).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanniel\OneDrive - amazon.com\桌面\2025 Q4 SSP benefits\Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50F2DDE-0377-4789-B11B-C4C46079283E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266892C9-F6FA-4D90-B8D5-FFD0DA635E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="720" windowWidth="19180" windowHeight="10080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
@@ -510,9 +510,6 @@
   <si>
     <t>品牌打造入門學｜優惠價：$199 USD，原價：$1600 USD 
 https://trb.one/Seller-Boost-Camp</t>
-  </si>
-  <si>
-    <t>商品頁內容優化方案，協助您進行視覺內容企劃，並執行產品競品分析，進一步撰寫圖片文案，客製化設計產品主子圖與 Basic A+: 優惠價$59,999元 (原價$65,000元)</t>
   </si>
   <si>
     <t>產品合規</t>
@@ -741,10 +738,6 @@
     <t>泰電國際</t>
   </si>
   <si>
-    <t>1) 0-1孵化器專案NTD: 30,000 (一次服務方案)
-2) 廣告投放專案NTD: 15,000/月 (最短合作時間需3個月)</t>
-  </si>
-  <si>
     <t>https://dolphinecommerce.com/</t>
   </si>
   <si>
@@ -770,7 +763,49 @@
     <t xml:space="preserve">0958-652-960 </t>
   </si>
   <si>
-    <t>【美國站跨境入門優惠方案】 專為美國市場拓展打造，現省 20 萬，加速啟動跨境布局！
+    <t>跨境物流 &amp; 海外倉</t>
+  </si>
+  <si>
+    <t>① AI影像廣告素材:NT$12,000/支 (企劃一次修改,AI完整生成)
+② 創意影音(依腳本內容定價)
+(以下圖片點擊放大)</t>
+  </si>
+  <si>
+    <t>EENuRetail 壹壹新零售</t>
+  </si>
+  <si>
+    <t>我們專注數據化、智能化的電商運營及媒體成效，並開創新型態TSP (Trade-Service-Partnership) 貿易型服務夥伴模式，協助合作夥伴零門檻打開國際市場，結合傳統貿易與專業服務，依照工廠不同狀態與需求，提供雙贏合作路徑 (亞馬遜運營服務 / B2C選物通路貿易 / B2B代工貼牌貿易)，協助台灣製造業工廠與品牌快速打開國際市場。</t>
+  </si>
+  <si>
+    <t>https://eenuretail.com/</t>
+  </si>
+  <si>
+    <t>Cindy</t>
+  </si>
+  <si>
+    <t>cindy@eenuretail.com</t>
+  </si>
+  <si>
+    <t>(以下圖片點擊放大)
+專案類型	走期天數	策略目標
+【流量啟動專案】	60天	快速測品、獲取首波數據
+【滾動穩健專案】	90天	穩型優化、擴張受眾規模
+【品牌全域專案】	180天	多點佈局、提升獲客成本
+限時促銷活動
+① 1/21-1/23 簽約 享 服務費10%
+② 陪跑計劃期間內簽約 享 服務費12%
+③ 指定Amazon DSP 獨立加碼 US$3,199 贈《AI影音廣告素材》一支
+註1:報價簽完後需一個月內儲值 註2:儲值金保有一年效益,專案經啟動後,天數不可中斷 註3:非促銷活動內,服務費一律15%</t>
+  </si>
+  <si>
+    <t>【商品頁內容優化方案】增添視覺新亮點，加速拓展新市場！
+專案價格：優惠價$59,999元/次 (原價$65,000元)
+專案對象：新銳品牌加速器、陪跑企劃賣家
+核心服務：視覺內容企劃、產品競品分析、圖片文案撰寫
+品牌優化：客製化設計產品主子圖與 Basic A+</t>
+  </si>
+  <si>
+    <t>【美國站跨境入門優惠方案】 專為拓展美國市場打造，現省 20 萬，加速啟動跨境布局！
 專案價格： $36,000 + 3% 服務抽成/月
 專案對象：新銳品牌加速器、陪跑企劃賣家
 核心服務：亞馬遜美國站管理、動態監控、市場調研與競品分析。
@@ -786,39 +821,8 @@
 價值增值： 積極對接政府補助資源中，細節確認後將第一時間為本方案客戶優先配對。</t>
   </si>
   <si>
-    <t>跨境物流 &amp; 海外倉</t>
-  </si>
-  <si>
-    <t>① AI影像廣告素材:NT$12,000/支 (企劃一次修改,AI完整生成)
-② 創意影音(依腳本內容定價)
-(以下圖片點擊放大)</t>
-  </si>
-  <si>
-    <t>EENuRetail 壹壹新零售</t>
-  </si>
-  <si>
-    <t>我們專注數據化、智能化的電商運營及媒體成效，並開創新型態TSP (Trade-Service-Partnership) 貿易型服務夥伴模式，協助合作夥伴零門檻打開國際市場，結合傳統貿易與專業服務，依照工廠不同狀態與需求，提供雙贏合作路徑 (亞馬遜運營服務 / B2C選物通路貿易 / B2B代工貼牌貿易)，協助台灣製造業工廠與品牌快速打開國際市場。</t>
-  </si>
-  <si>
-    <t>https://eenuretail.com/</t>
-  </si>
-  <si>
-    <t>Cindy</t>
-  </si>
-  <si>
-    <t>cindy@eenuretail.com</t>
-  </si>
-  <si>
-    <t>(以下圖片點擊放大)
-專案類型	走期天數	策略目標
-【流量啟動專案】	60天	快速測品、獲取首波數據
-【滾動穩健專案】	90天	穩型優化、擴張受眾規模
-【品牌全域專案】	180天	多點佈局、提升獲客成本
-限時促銷活動
-① 1/21-1/23 簽約 享 服務費10%
-② 陪跑計劃期間內簽約 享 服務費12%
-③ 指定Amazon DSP 獨立加碼 US$3,199 贈《AI影音廣告素材》一支
-註1:報價簽完後需一個月內儲值 註2:儲值金保有一年效益,專案經啟動後,天數不可中斷 註3:非促銷活動內,服務費一律15%</t>
+    <t>1) 0-1孵化器專案NTD: 30,000 (一次服務方案)
+2) 廣告投放專案NTD: 15,000/月+實收服務費 3% (最短合作時間需3個月)</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1086,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1207,19 +1211,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1602,7 +1602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>61</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>64</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F2" s="29"/>
       <c r="G2" s="4" t="s">
@@ -1652,7 +1652,7 @@
         <v>64</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G3" s="33" t="s">
         <v>147</v>
@@ -1685,7 +1685,7 @@
         <v>45</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="F4" s="24"/>
       <c r="G4" s="1" t="s">
@@ -1698,46 +1698,46 @@
         <v>28</v>
       </c>
       <c r="J4" s="44" t="s">
+        <v>191</v>
+      </c>
+      <c r="K4" s="44" t="s">
         <v>192</v>
       </c>
-      <c r="K4" s="44" t="s">
-        <v>193</v>
-      </c>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="212.5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>199</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="F5" s="24"/>
+      <c r="G5" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="F5" s="24"/>
-      <c r="G5" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="H5" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I5" s="24"/>
       <c r="J5" s="8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="3"/>
     </row>
     <row r="6" spans="1:12" ht="62.5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>129</v>
@@ -1749,7 +1749,7 @@
         <v>45</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>132</v>
@@ -1805,31 +1805,31 @@
     </row>
     <row r="8" spans="1:12" ht="162.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>212</v>
+        <v>213</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>209</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="50" t="s">
-        <v>217</v>
-      </c>
-      <c r="F8" s="49"/>
-      <c r="G8" s="48" t="s">
-        <v>213</v>
+      <c r="E8" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="F8" s="29"/>
+      <c r="G8" s="47" t="s">
+        <v>210</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="I8" s="51"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="53"/>
+        <v>211</v>
+      </c>
+      <c r="I8" s="49"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="51"/>
     </row>
     <row r="9" spans="1:12" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1842,7 +1842,7 @@
         <v>14</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>15</v>
@@ -1878,10 +1878,10 @@
         <v>112</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
@@ -1901,19 +1901,19 @@
     </row>
     <row r="11" spans="1:12" ht="50" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>194</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>195</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>40</v>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" ht="62.5" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1944,10 +1944,10 @@
         <v>24</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>155</v>
+        <v>159</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>215</v>
       </c>
       <c r="F12" s="24" t="s">
         <v>25</v>
@@ -1962,10 +1962,10 @@
         <v>28</v>
       </c>
       <c r="J12" s="44" t="s">
+        <v>191</v>
+      </c>
+      <c r="K12" s="44" t="s">
         <v>192</v>
-      </c>
-      <c r="K12" s="44" t="s">
-        <v>193</v>
       </c>
       <c r="L12" s="27" t="s">
         <v>29</v>
@@ -1973,30 +1973,30 @@
     </row>
     <row r="13" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C13" s="47" t="s">
-        <v>212</v>
+        <v>213</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>209</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E13" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="F13" s="24"/>
+      <c r="G13" s="47" t="s">
+        <v>210</v>
+      </c>
+      <c r="H13" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="F13" s="24"/>
-      <c r="G13" s="48" t="s">
-        <v>213</v>
-      </c>
-      <c r="H13" s="24" t="s">
-        <v>214</v>
-      </c>
       <c r="I13" s="24"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
       <c r="L13" s="27"/>
     </row>
     <row r="14" spans="1:12" ht="25" x14ac:dyDescent="0.25">
@@ -2010,10 +2010,10 @@
         <v>90</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F14" s="24" t="s">
         <v>97</v>
@@ -2046,10 +2046,10 @@
         <v>90</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F15" s="25" t="s">
         <v>91</v>
@@ -2085,7 +2085,7 @@
         <v>58</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>74</v>
@@ -2114,8 +2114,8 @@
       <c r="D17" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="14" t="s">
-        <v>161</v>
+      <c r="E17" s="15" t="s">
+        <v>160</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -2131,72 +2131,72 @@
     </row>
     <row r="18" spans="1:12" ht="50" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B18" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="C18" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="D18" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E18" s="14" t="s">
         <v>174</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>175</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="H18" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="H18" s="25" t="s">
+      <c r="I18" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="I18" s="25" t="s">
+      <c r="J18" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="J18" s="30" t="s">
+      <c r="K18" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="K18" s="18" t="s">
+      <c r="L18" s="31" t="s">
         <v>180</v>
-      </c>
-      <c r="L18" s="31" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="137.5" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="C19" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="D19" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E19" s="14" t="s">
         <v>184</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>185</v>
       </c>
       <c r="F19" s="35"/>
       <c r="G19" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="I19" s="35"/>
       <c r="J19" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="K19" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="K19" s="17" t="s">
+      <c r="L19" s="42" t="s">
         <v>189</v>
-      </c>
-      <c r="L19" s="42" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="13" x14ac:dyDescent="0.25">
@@ -2210,7 +2210,7 @@
         <v>121</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E20" s="21" t="s">
         <v>122</v>
@@ -2246,10 +2246,10 @@
         <v>139</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F21" s="36" t="s">
         <v>140</v>
@@ -2264,7 +2264,7 @@
         <v>143</v>
       </c>
       <c r="J21" s="45" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K21" s="11">
         <v>8166826864</v>
@@ -2281,7 +2281,7 @@
         <v>48</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E22" s="21" t="s">
         <v>49</v>
@@ -2315,10 +2315,10 @@
         <v>102</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>103</v>
@@ -2392,7 +2392,7 @@
         <v>152</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>79</v>
@@ -2422,7 +2422,7 @@
         <v>153</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F26" s="24" t="s">
         <v>81</v>
@@ -2452,7 +2452,7 @@
         <v>153</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F27" s="25" t="s">
         <v>84</v>
@@ -2476,13 +2476,13 @@
         <v>72</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D28" s="18" t="s">
         <v>153</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>86</v>
@@ -2509,10 +2509,10 @@
         <v>73</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F29" s="24" t="s">
         <v>77</v>

--- a/[服務商優惠徵集 ] 智造在台灣6.0 & 亞馬遜新銳品牌加速器2.0 (Responses)(2).xlsx
+++ b/[服務商優惠徵集 ] 智造在台灣6.0 & 亞馬遜新銳品牌加速器2.0 (Responses)(2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanniel\OneDrive - amazon.com\桌面\2025 Q4 SSP benefits\Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266892C9-F6FA-4D90-B8D5-FFD0DA635E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D841289E-2186-4C79-8447-2A102DE12454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="720" windowWidth="19180" windowHeight="10080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
@@ -2266,9 +2266,7 @@
       <c r="J21" s="45" t="s">
         <v>206</v>
       </c>
-      <c r="K21" s="11">
-        <v>8166826864</v>
-      </c>
+      <c r="K21" s="11"/>
     </row>
     <row r="22" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
